--- a/data/raw/inventory/Week 32/Nexlev/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 32/Nexlev/Seller FBA Inventory (SP-API).xlsx
@@ -1140,7 +1140,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F12" t="n">
         <v>344</v>
@@ -1155,10 +1155,10 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K12" t="n">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F13" t="n">
         <v>371</v>
@@ -1217,10 +1217,10 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K13" t="n">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="L13" t="n">
         <v>12</v>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F22" t="n">
         <v>215</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L22" t="n">
         <v>1</v>
@@ -2256,10 +2256,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F30" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2274,7 +2274,7 @@
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -4426,7 +4426,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F65" t="n">
         <v>66</v>
@@ -4441,10 +4441,10 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K65" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L65" t="n">
         <v>3</v>
@@ -4615,7 +4615,7 @@
         <v>164</v>
       </c>
       <c r="F68" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -4627,7 +4627,7 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K68" t="n">
         <v>188</v>
@@ -4925,7 +4925,7 @@
         <v>35</v>
       </c>
       <c r="F73" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -4937,7 +4937,7 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
         <v>35</v>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F99" t="n">
         <v>13</v>
@@ -6549,10 +6549,10 @@
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K99" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L99" t="n">
         <v>1</v>
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
@@ -7355,10 +7355,10 @@
         <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K112" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L112" t="n">
         <v>10</v>
@@ -8394,7 +8394,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F129" t="n">
         <v>154</v>
@@ -8409,10 +8409,10 @@
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K129" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L129" t="n">
         <v>1</v>
@@ -9823,7 +9823,7 @@
         <v>94</v>
       </c>
       <c r="F152" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -9835,7 +9835,7 @@
         <v>0</v>
       </c>
       <c r="J152" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K152" t="n">
         <v>94</v>
@@ -9944,7 +9944,7 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F154" t="n">
         <v>78</v>
@@ -9959,10 +9959,10 @@
         <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L154" t="n">
         <v>5</v>
@@ -10874,7 +10874,7 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F169" t="n">
         <v>6</v>
@@ -10889,10 +10889,10 @@
         <v>0</v>
       </c>
       <c r="J169" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K169" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L169" t="n">
         <v>13</v>
@@ -11621,7 +11621,7 @@
         <v>21</v>
       </c>
       <c r="F181" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -11633,7 +11633,7 @@
         <v>0</v>
       </c>
       <c r="J181" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K181" t="n">
         <v>22</v>
